--- a/vendor_application_form_templates/025_sustainable_supply_chain_initiative_application_form--vendor_application_form_templates.xlsx
+++ b/vendor_application_form_templates/025_sustainable_supply_chain_initiative_application_form--vendor_application_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1171,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>alaska</t>
+          <t>american_samoa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>American Samoa</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>american_samoa</t>
+          <t>arizona</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>American Samoa</t>
+          <t>Arizona</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>arizona</t>
+          <t>arkansas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>Arkansas</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>arkansas</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>california</t>
+          <t>colorado</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Colorado</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>colorado</t>
+          <t>connecticut</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Connecticut</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>connecticut</t>
+          <t>delaware</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Delaware</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>delaware</t>
+          <t>district_of_columbia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Delaware</t>
+          <t>District of Columbia</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>district_of_columbia</t>
+          <t>florida</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>District of Columbia</t>
+          <t>Florida</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>florida</t>
+          <t>georgia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Georgia</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>georgia</t>
+          <t>guam</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Guam</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>guam</t>
+          <t>hawaii</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Guam</t>
+          <t>Hawaii</t>
         </is>
       </c>
     </row>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hawaii</t>
+          <t>idaho</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>Idaho</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>idaho</t>
+          <t>illinois</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Illinois</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>illinois</t>
+          <t>indiana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Indiana</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>indiana</t>
+          <t>iowa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Iowa</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>iowa</t>
+          <t>kansas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Kansas</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>kansas</t>
+          <t>kentucky</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Kentucky</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>kentucky</t>
+          <t>louisiana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Louisiana</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>louisiana</t>
+          <t>maine</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Louisiana</t>
+          <t>Maine</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>maine</t>
+          <t>maryland</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Maine</t>
+          <t>Maryland</t>
         </is>
       </c>
     </row>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>maryland</t>
+          <t>massachusetts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Massachusetts</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>massachusetts</t>
+          <t>michigan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Michigan</t>
         </is>
       </c>
     </row>
@@ -1629,12 +1629,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>michigan</t>
+          <t>minnesota</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Minnesota</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>minnesota</t>
+          <t>mississippi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Mississippi</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>mississippi</t>
+          <t>missouri</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>Missouri</t>
         </is>
       </c>
     </row>
@@ -1680,12 +1680,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>missouri</t>
+          <t>montana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Montana</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>montana</t>
+          <t>nebraska</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Nebraska</t>
         </is>
       </c>
     </row>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nebraska</t>
+          <t>nevada</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Nevada</t>
         </is>
       </c>
     </row>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nevada</t>
+          <t>new_hampshire</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>New Hampshire</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>new_hampshire</t>
+          <t>new_jersey</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>New Jersey</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1765,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>new_jersey</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>new_york</t>
+          <t>north_carolina</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>North Carolina</t>
         </is>
       </c>
     </row>
@@ -1799,12 +1799,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>north_carolina</t>
+          <t>north_dakota</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>North Dakota</t>
         </is>
       </c>
     </row>
@@ -1816,12 +1816,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>north_dakota</t>
+          <t>ohio</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>Ohio</t>
         </is>
       </c>
     </row>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ohio</t>
+          <t>oklahoma</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Oklahoma</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>oklahoma</t>
+          <t>oregon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Oregon</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>oregon</t>
+          <t>pennsylvania</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
     </row>
@@ -1884,12 +1884,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>pennsylvania</t>
+          <t>puerto_rico</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>puerto_rico</t>
+          <t>rhode_island</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Rhode Island</t>
         </is>
       </c>
     </row>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>rhode_island</t>
+          <t>south_carolina</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>South Carolina</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>south_carolina</t>
+          <t>south_dakota</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>South Dakota</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>south_dakota</t>
+          <t>tennessee</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>South Dakota</t>
+          <t>Tennessee</t>
         </is>
       </c>
     </row>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>tennessee</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>texas</t>
+          <t>utah</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Utah</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>utah</t>
+          <t>vermont</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Utah</t>
+          <t>Vermont</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>vermont</t>
+          <t>virgin_islands</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vermont</t>
+          <t>Virgin Islands</t>
         </is>
       </c>
     </row>
@@ -2037,12 +2037,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>virgin_islands</t>
+          <t>virginia</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Virgin Islands</t>
+          <t>Virginia</t>
         </is>
       </c>
     </row>
@@ -2054,12 +2054,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>virginia</t>
+          <t>washington</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Washington</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>washington</t>
+          <t>west_virginia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>West Virginia</t>
         </is>
       </c>
     </row>
@@ -2088,12 +2088,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>west_virginia</t>
+          <t>wisconsin</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Wisconsin</t>
         </is>
       </c>
     </row>
@@ -2105,27 +2105,10 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>wisconsin</t>
+          <t>wyoming</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
-        <is>
-          <t>Wisconsin</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>state_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>wyoming</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
         <is>
           <t>Wyoming</t>
         </is>
